--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.18507798035323</v>
+        <v>8.805075171807401</v>
       </c>
       <c r="D2" t="n">
-        <v>64.02160724175404</v>
+        <v>10.40351117678503</v>
       </c>
       <c r="E2" t="n">
-        <v>19.80014872818283</v>
+        <v>3.217524168329711</v>
       </c>
       <c r="F2" t="n">
-        <v>15.19910333578321</v>
+        <v>2.469854292064772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.0757765568799</v>
+        <v>12.03731369049298</v>
       </c>
       <c r="D3" t="n">
-        <v>73.53495862759542</v>
+        <v>11.94943077698426</v>
       </c>
       <c r="E3" t="n">
-        <v>19.80014872818283</v>
+        <v>3.217524168329711</v>
       </c>
       <c r="F3" t="n">
-        <v>15.19910333578321</v>
+        <v>2.469854292064772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.84899415085236</v>
+        <v>3.062961549513508</v>
       </c>
       <c r="D4" t="n">
-        <v>39.30911625671384</v>
+        <v>6.387731391715999</v>
       </c>
       <c r="E4" t="n">
-        <v>19.80014872818283</v>
+        <v>3.217524168329711</v>
       </c>
       <c r="F4" t="n">
-        <v>15.19910333578321</v>
+        <v>2.469854292064772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.89969521408393</v>
+        <v>7.621200472288638</v>
       </c>
       <c r="D5" t="n">
-        <v>38.96041076627431</v>
+        <v>6.331066749519575</v>
       </c>
       <c r="E5" t="n">
-        <v>19.80014872818283</v>
+        <v>3.217524168329711</v>
       </c>
       <c r="F5" t="n">
-        <v>15.19910333578321</v>
+        <v>2.469854292064772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
